--- a/output/Timetable_Odd_Sem_2026.xlsx
+++ b/output/Timetable_Odd_Sem_2026.xlsx
@@ -526,13 +526,13 @@
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -554,20 +554,25 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Introduction to AI and its Applications
 (Seema H R)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 (Dr. C Balarengadurai)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+(Dr. C Balarengadurai)</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
     </row>
@@ -578,8 +583,18 @@
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(Seema H R)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Dr. C Balarengadurai)</t>
+        </is>
+      </c>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
@@ -590,24 +605,14 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-(Dr. C Balarengadurai)</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 (Dr. C Balarengadurai)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(Seema H R)</t>
-        </is>
-      </c>
+      <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
@@ -631,12 +636,7 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Dr. C Balarengadurai)</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
@@ -690,13 +690,13 @@
       <c r="D12" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -718,18 +718,8 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Dr. C Manjunath)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(Revathy B D)</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
@@ -754,15 +744,10 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Programming in C
-(Dr. C Manjunath)</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
 (Dr. C Manjunath)</t>
         </is>
       </c>
@@ -777,20 +762,25 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Introduction to AI and its Applications
 (Revathy B D)</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+(Dr. C Manjunath)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 (Dr. C Manjunath)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
     </row>
@@ -813,8 +803,18 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Dr. C Manjunath)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(Revathy B D)</t>
+        </is>
+      </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
@@ -854,13 +854,13 @@
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -882,24 +882,9 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(Vignesh T V)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-(Prashanth N)</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Prashanth N)</t>
-        </is>
-      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
@@ -911,18 +896,8 @@
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Prashanth N)</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(Vignesh T V)</t>
-        </is>
-      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
@@ -936,11 +911,16 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
+          <t>Programming in C Laboratory
+(Prashanth N)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
           <t>Programming in C
 (Prashanth N)</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
@@ -952,8 +932,18 @@
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Prashanth N)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(Vignesh T V)</t>
+        </is>
+      </c>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
@@ -965,8 +955,18 @@
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Prashanth N)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(Vignesh T V)</t>
+        </is>
+      </c>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
@@ -1018,13 +1018,13 @@
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1053,7 +1053,12 @@
 (Nidhishree G)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(Gaurav)</t>
+        </is>
+      </c>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
@@ -1064,24 +1069,9 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(Gaurav)</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-(Nidhishree G)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Nidhishree G)</t>
-        </is>
-      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
@@ -1093,9 +1083,24 @@
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+(Nidhishree G)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Nidhishree G)</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(Gaurav)</t>
+        </is>
+      </c>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
     </row>
@@ -1106,18 +1111,8 @@
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Nidhishree G)</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(Gaurav)</t>
-        </is>
-      </c>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
@@ -1142,7 +1137,12 @@
         </is>
       </c>
       <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Nidhishree G)</t>
+        </is>
+      </c>
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
@@ -1182,13 +1182,13 @@
       <c r="D39" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1211,12 +1211,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Mohan Kumar G)</t>
-        </is>
-      </c>
+      <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="n"/>
       <c r="F40" s="6" t="n"/>
@@ -1228,12 +1223,7 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-(Mohan Kumar G)</t>
-        </is>
-      </c>
+      <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Programming in C
@@ -1256,19 +1246,19 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Mohan Kumar G)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Introduction to AI and its Applications
 (New Faculty 1)</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(Mohan Kumar G)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n"/>
       <c r="E42" s="6" t="n"/>
       <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
@@ -1293,8 +1283,18 @@
         </is>
       </c>
       <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(Mohan Kumar G)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+(Mohan Kumar G)</t>
+        </is>
+      </c>
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
@@ -1346,13 +1346,13 @@
       <c r="D48" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -1374,24 +1374,14 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(New Faculty 4)</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 (K B Manasa)</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-(K B Manasa)</t>
-        </is>
-      </c>
+      <c r="D49" s="6" t="n"/>
       <c r="E49" s="6" t="n"/>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n"/>
@@ -1402,18 +1392,8 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-(New Faculty 4)</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(K B Manasa)</t>
-        </is>
-      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
       <c r="D50" s="6" t="n"/>
       <c r="E50" s="6" t="n"/>
       <c r="F50" s="6" t="n"/>
@@ -1425,8 +1405,18 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(New Faculty 4)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(K B Manasa)</t>
+        </is>
+      </c>
       <c r="D51" s="6" t="n"/>
       <c r="E51" s="6" t="n"/>
       <c r="F51" s="6" t="n"/>
@@ -1452,9 +1442,24 @@
         </is>
       </c>
       <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+(K B Manasa)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+(K B Manasa)</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+(New Faculty 4)</t>
+        </is>
+      </c>
       <c r="F53" s="6" t="n"/>
       <c r="G53" s="6" t="n"/>
     </row>
@@ -1465,12 +1470,7 @@
         </is>
       </c>
       <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-(K B Manasa)</t>
-        </is>
-      </c>
+      <c r="C54" s="6" t="n"/>
       <c r="D54" s="6" t="n"/>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="6" t="n"/>
@@ -1517,13 +1517,13 @@
       <c r="D58" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -1545,11 +1545,36 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+(Seema H R)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+(Prashanth N)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+(Dr. Prashanth M V)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+(Dr. Prashanth M V)</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+(Dr. Prashanth M V)</t>
+        </is>
+      </c>
       <c r="G59" s="6" t="n"/>
     </row>
     <row r="60">
@@ -1558,36 +1583,31 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Operating System
 (Prashanth N)</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Oops with Java
 (Seema H R)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Java Laboratory
 (Seema H R)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Java Laboratory
 (Seema H R)</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>UHV
-(Indu J)</t>
-        </is>
-      </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Data Structures
@@ -1601,8 +1621,18 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+(Prashanth N)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+(Seema H R)</t>
+        </is>
+      </c>
       <c r="D61" s="6" t="n"/>
       <c r="E61" s="6" t="n"/>
       <c r="F61" s="6" t="n"/>
@@ -1616,34 +1646,19 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Operating System
-(Prashanth N)</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-(Seema H R)</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
           <t>Data Structures
 (Dr. Prashanth M V)</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-(Dr. Prashanth M V)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-(Dr. Prashanth M V)</t>
-        </is>
-      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>UHV
+(Indu J)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
       <c r="G62" s="6" t="n"/>
     </row>
     <row r="63">
@@ -1665,24 +1680,9 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-(Dr. Prashanth M V)</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-(Prashanth N)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-(Seema H R)</t>
-        </is>
-      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
       <c r="E64" s="6" t="n"/>
       <c r="F64" s="6" t="n"/>
       <c r="G64" s="6" t="n"/>
@@ -1721,13 +1721,13 @@
       <c r="D67" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -1757,109 +1757,94 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
+          <t>Oops with Java
+(Revathy B D)</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+(Revathy B D)</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+(Revathy B D)</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+(Indu J)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+(Indu J)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+(Revathy B D)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+(Nidhishree G)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
           <t>Web App Development
 (Dr. Pramila R M)</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+(Indu J)</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+(Indu J)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Oops with Java
 (Revathy B D)</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-(Indu J)</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>UHV
-(Soumya G V)</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-(Nidhishree G)</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Web App Development
 (Dr. Pramila R M)</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-(Indu J)</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-(Indu J)</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-(Revathy B D)</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-(Indu J)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-(Indu J)</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-(Nidhishree G)</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-(Revathy B D)</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-(Revathy B D)</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-(Revathy B D)</t>
-        </is>
-      </c>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
       <c r="G70" s="6" t="n"/>
     </row>
     <row r="71">
@@ -1881,9 +1866,24 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>UHV
+(Soumya G V)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+(Nidhishree G)</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+(Indu J)</t>
+        </is>
+      </c>
       <c r="E72" s="6" t="n"/>
       <c r="F72" s="6" t="n"/>
       <c r="G72" s="6" t="n"/>
@@ -1935,13 +1935,13 @@
       <c r="D76" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -1965,149 +1965,149 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
+          <t>Data Structures
+(Vignesh T V)</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+(Vignesh T V)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+(Vignesh T V)</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+(Latha D U)</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+(Rachana S)</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+(Rashmi K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
           <t>Design Thinking
 (Mohan Kumar G)</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+(Rachana S)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+(Latha D U)</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>Data Structures
 (Vignesh T V)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>UHV
+(New Faculty 2)</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+(Rashmi K)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
 (Vignesh T V)</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-(Vignesh T V)</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Design Thinking
+(Mohan Kumar G)</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>Operating System
 (Rachana S)</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="F79" s="6" t="n"/>
+      <c r="G79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>IoT Skill Lab
+(Soumya G V)</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>IoT Skill Lab
+(Soumya G V)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+(Rashmi K)</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+(Rashmi K)</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Oops with Java
 (Rashmi K)</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-(Rashmi K)</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-(Rashmi K)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-(Rashmi K)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>IoT Skill Lab
-(Soumya G V)</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>IoT Skill Lab
-(Soumya G V)</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-(Rachana S)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-(Latha D U)</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-(Vignesh T V)</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>UHV
-(New Faculty 2)</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="6" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-(Vignesh T V)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-(Rachana S)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-(Latha D U)</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>Design Thinking
-(Mohan Kumar G)</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-(Rashmi K)</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -2176,13 +2176,13 @@
       <c r="D86" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -2206,156 +2206,166 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
+          <t>Cryptography and Network Security
+(New Faculty 1)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
           <t>Machine Learning
 (Dr. Varshitha D N)</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Cloud Computing
+(Harshith V)</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+(Harshith C)</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+(Dr. Vijay C P)</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Cloud Computing
+(Harshith V)</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+(Dr. Varshitha D N)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+(Harshith C)</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+(New Faculty 1)</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+(Dr. Vijay C P)</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+(Dr. Varshitha D N)</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>Machine Learning Lab
 (Dr. Varshitha D N)</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>Machine Learning Lab
 (Dr. Varshitha D N)</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+(Harshith C)</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+(Dr. Vijay C P)</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+(New Faculty 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>RMIPR
+(Dr. C Balarengadurai)</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>Cloud Computing
 (Harshith V)</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Harshith C)</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-(New Faculty 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-(Dr. Varshitha D N)</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Computing
-(Harshith V)</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 (Dr. Vijay C P)</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>RMIPR
-(Dr. C Balarengadurai)</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="6" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Harshith C)</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-(Dr. Vijay C P)</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-(Dr. Varshitha D N)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>DevOps Laboratory
 (Dr. Aditya C R)</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>DevOps Laboratory
 (Dr. Aditya C R)</t>
         </is>
       </c>
-      <c r="G89" s="6" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="6" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Harshith C)</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-(New Faculty 1)</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Computing
-(Harshith V)</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-(Dr. Vijay C P)</t>
-        </is>
-      </c>
-      <c r="F91" s="6" t="n"/>
       <c r="G91" s="6" t="n"/>
     </row>
     <row r="92">
@@ -2364,18 +2374,8 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-(Dr. Vijay C P)</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-(New Faculty 1)</t>
-        </is>
-      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
       <c r="D92" s="6" t="n"/>
       <c r="E92" s="6" t="n"/>
       <c r="F92" s="6" t="n"/>
@@ -2415,13 +2415,13 @@
       <c r="D95" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -2449,135 +2449,155 @@
 (Dr. Pramila R M)</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lab
+(Dr. Pramila R M)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lab
+(Dr. Pramila R M)</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Web App Development
 (Pooja N S)</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning Lab
-(Dr. Pramila R M)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning Lab
-(Dr. Pramila R M)</t>
-        </is>
-      </c>
       <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+(New Faculty 4)</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 (New Faculty 2)</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+(Pooja N S)</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+(Dr. Pramila R M)</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>RMIPR
+(Dr. C Manjunath)</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+(New Faculty 4)</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>Management and Engineering Economics
 (Gaurav)</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 (New Faculty 2)</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+(New Faculty 2)</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+(Dr. Pramila R M)</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+(Dr. Vijay C P)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+(Dr. Vijay C P)</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+(Gaurav)</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+(Gaurav)</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+(New Faculty 2)</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>Cryptography and Network Security
 (New Faculty 4)</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Gaurav)</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>RMIPR
-(Dr. C Manjunath)</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="6" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-(Dr. Pramila R M)</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-(Pooja N S)</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-(Dr. Vijay C P)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-(Dr. Vijay C P)</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-(New Faculty 2)</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-(New Faculty 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="6" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
       <c r="E100" s="6" t="n"/>
       <c r="F100" s="6" t="n"/>
       <c r="G100" s="6" t="n"/>
@@ -2588,30 +2608,10 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Gaurav)</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-(Dr. Pramila R M)</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-(New Faculty 2)</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-(New Faculty 4)</t>
-        </is>
-      </c>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
       <c r="F101" s="6" t="n"/>
       <c r="G101" s="6" t="n"/>
     </row>
@@ -2649,13 +2649,13 @@
       <c r="D104" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -2677,138 +2677,133 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+(Latha D U)</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>Machine Learning Lab
 (Latha D U)</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Machine Learning Lab
 (Latha D U)</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>Web App Development
 (Shruthi B S)</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Open Elective (Basics of AI/ML)
+(Dr. Sonali Nandish Manoli)</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+(Rachana S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+(New Faculty 3)</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Open Elective (Basics of AI/ML)
+(Dr. Sonali Nandish Manoli)</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+(Rashmi K)</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+(Rashmi K)</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>RMIPR
+(Dr. Prashanth M V)</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>Machine Learning
 (Latha D U)</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 (New Faculty 3)</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+(Shruthi B S)</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="n"/>
+      <c r="G107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Open Elective (Basics of AI/ML)
+(Dr. Sonali Nandish Manoli)</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>Management and Engineering Economics
 (Rachana S)</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 (New Faculty 3)</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-(Latha D U)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-(Shruthi B S)</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>Open Elective (Basics of AI/ML)
-(Dr. Sonali Nandish Manoli)</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>RMIPR
-(Dr. Prashanth M V)</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Rachana S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-(Latha D U)</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-(Rachana S)</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>Open Elective (Basics of AI/ML)
-(Dr. Sonali Nandish Manoli)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-(Rashmi K)</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-(Rashmi K)</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-(New Faculty 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
       <c r="E108" s="6" t="n"/>
       <c r="F108" s="6" t="n"/>
       <c r="G108" s="6" t="n"/>
@@ -2821,17 +2816,22 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Open Elective (Basics of AI/ML)
-(Dr. Sonali Nandish Manoli)</t>
+          <t>Management and Engineering Economics
+(Rachana S)</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+(Latha D U)</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 (New Faculty 3)</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n"/>
       <c r="E109" s="6" t="n"/>
       <c r="F109" s="6" t="n"/>
       <c r="G109" s="6" t="n"/>
@@ -2890,13 +2890,13 @@
       <c r="D114" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -2931,22 +2931,17 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 (Pooja N S)</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Natural Language Processing
-(Dr. Varshitha D N)</t>
-        </is>
-      </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Pattern Recognition
-(Harshith C)</t>
+          <t>Big Data Analytics
+(Soumya G V)</t>
         </is>
       </c>
       <c r="E116" s="6" t="n"/>
@@ -2960,10 +2955,30 @@
         </is>
       </c>
       <c r="B117" s="6" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="n"/>
-      <c r="E117" s="6" t="n"/>
-      <c r="F117" s="6" t="n"/>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+(Dr. Varshitha D N)</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>NoSQL Database
+(Pooja N S)</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+(Harshith C)</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Big Data Analytics
+(Soumya G V)</t>
+        </is>
+      </c>
       <c r="G117" s="6" t="n"/>
     </row>
     <row r="118">
@@ -2972,84 +2987,69 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="n"/>
+      <c r="F118" s="6" t="n"/>
+      <c r="G118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n"/>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+(Dr. Varshitha D N)</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 (Pooja N S)</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>Pattern Recognition
 (Harshith C)</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="F119" s="6" t="n"/>
+      <c r="G119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+(Harshith C)</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>Natural Language Processing
 (Dr. Varshitha D N)</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>NoSQL Database
+(Pooja N S)</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
         <is>
           <t>Big Data Analytics
 (Soumya G V)</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>Big Data Analytics
-(Soumya G V)</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>NoSQL Database
-(Pooja N S)</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="n"/>
-      <c r="E119" s="6" t="n"/>
-      <c r="F119" s="6" t="n"/>
-      <c r="G119" s="6" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>Big Data Analytics
-(Soumya G V)</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>Natural Language Processing
-(Dr. Varshitha D N)</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>NoSQL Database
-(Pooja N S)</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>Pattern Recognition
-(Harshith C)</t>
         </is>
       </c>
       <c r="F120" s="6" t="n"/>
@@ -3089,13 +3089,13 @@
       <c r="D123" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -3125,22 +3125,17 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Natural Language Processing
-(Dr. Sonali Nandish Manoli)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
           <t>Pattern Recognition
 (Harshith V)</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 (Shruthi B S)</t>
         </is>
       </c>
+      <c r="E124" s="6" t="n"/>
       <c r="F124" s="6" t="n"/>
       <c r="G124" s="6" t="n"/>
     </row>
@@ -3152,14 +3147,14 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Pattern Recognition
-(Harshith V)</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
           <t>NoSQL Database
 (Shruthi B S)</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX Design
+(K B Manasa)</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -3178,65 +3173,60 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B126" s="6" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+      <c r="E126" s="6" t="n"/>
+      <c r="F126" s="6" t="n"/>
+      <c r="G126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="n"/>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX Design
+(K B Manasa)</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 (Shruthi B S)</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>UI/UX Design
-(K B Manasa)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>Pattern Recognition
 (Harshith V)</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F127" s="6" t="n"/>
+      <c r="G127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>Natural Language Processing
 (Dr. Sonali Nandish Manoli)</t>
         </is>
       </c>
-      <c r="F126" s="6" t="n"/>
-      <c r="G126" s="6" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="n"/>
-      <c r="C127" s="6" t="n"/>
-      <c r="D127" s="6" t="n"/>
-      <c r="E127" s="6" t="n"/>
-      <c r="F127" s="6" t="n"/>
-      <c r="G127" s="6" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>UI/UX Design
-(K B Manasa)</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 (Shruthi B S)</t>
         </is>
       </c>
-      <c r="D128" s="6" t="n"/>
       <c r="E128" s="6" t="n"/>
       <c r="F128" s="6" t="n"/>
       <c r="G128" s="6" t="n"/>
@@ -3248,8 +3238,18 @@
         </is>
       </c>
       <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+(Dr. Sonali Nandish Manoli)</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+(Harshith V)</t>
+        </is>
+      </c>
       <c r="E129" s="6" t="n"/>
       <c r="F129" s="6" t="n"/>
       <c r="G129" s="6" t="n"/>
@@ -3305,13 +3305,13 @@
       <c r="D2" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -3362,18 +3362,8 @@
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-5th Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
@@ -3398,8 +3388,18 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+5th Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+5th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
@@ -3418,7 +3418,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Dr. C Balarengadurai   (5 h/week, 1st hour x2)</t>
+          <t>Dr. C Balarengadurai   (5 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -3443,13 +3443,13 @@
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -3472,14 +3472,19 @@
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 1st Sem - Sec A</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+1st Sem - Sec A</t>
+        </is>
+      </c>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
     </row>
@@ -3491,13 +3496,13 @@
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>RMIPR
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
     </row>
@@ -3507,12 +3512,7 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-1st Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Programming in C
@@ -3545,8 +3545,8 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Programming in C
-1st Sem - Sec A</t>
+          <t>RMIPR
+5th Sem - Sec A</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
@@ -3571,7 +3571,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Dr. C Manjunath   (5 h/week, 1st hour x2)</t>
+          <t>Dr. C Manjunath   (5 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -3596,13 +3596,13 @@
       <c r="D20" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3624,12 +3624,7 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
@@ -3644,13 +3639,13 @@
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>RMIPR
 5th Sem - Sec B</t>
         </is>
       </c>
+      <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
     </row>
@@ -3660,15 +3655,10 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Programming in C
-1st Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
 1st Sem - Sec B</t>
         </is>
       </c>
@@ -3684,14 +3674,19 @@
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+1st Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 1st Sem - Sec B</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
     </row>
@@ -3714,7 +3709,12 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec B</t>
+        </is>
+      </c>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
@@ -3724,7 +3724,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Dr. Pramila R M   (7 h/week, 1st hour x2)</t>
+          <t>Dr. Pramila R M   (7 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -3749,13 +3749,13 @@
       <c r="D29" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -3783,41 +3783,41 @@
 5th Sem - Sec B</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lab
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lab
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Web App Development
 3rd Sem - Sec B</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning Lab
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning Lab
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-3rd Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
@@ -3828,14 +3828,14 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+3rd Sem - Sec B</t>
+        </is>
+      </c>
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
@@ -3847,7 +3847,12 @@
         </is>
       </c>
       <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+5th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
@@ -3873,12 +3878,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="C35" s="6" t="n"/>
       <c r="D35" s="6" t="n"/>
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
@@ -3912,13 +3912,13 @@
       <c r="D38" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3942,9 +3942,24 @@
       </c>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+3rd Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+3rd Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+3rd Sem - Sec A</t>
+        </is>
+      </c>
       <c r="G39" s="6" t="n"/>
     </row>
     <row r="40">
@@ -3989,26 +4004,16 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Data Structures
 3rd Sem - Sec A</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-3rd Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-3rd Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
     </row>
     <row r="43">
@@ -4030,12 +4035,7 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-3rd Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6" t="n"/>
       <c r="E44" s="6" t="n"/>
@@ -4070,13 +4070,13 @@
       <c r="D47" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4099,70 +4099,65 @@
         </is>
       </c>
       <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Open Elective (Basics of AI/ML)
+5th Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Open Elective (Basics of AI/ML)
+5th Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Natural Language Processing
 7th Sem - Sec B</t>
         </is>
       </c>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Natural Language Processing
-7th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Open Elective (Basics of AI/ML)
 5th Sem - Sec C</t>
         </is>
       </c>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Open Elective (Basics of AI/ML)
-5th Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Natural Language Processing
-7th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6" t="n"/>
       <c r="E51" s="6" t="n"/>
@@ -4175,13 +4170,13 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Open Elective (Basics of AI/ML)
-5th Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+7th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D52" s="6" t="n"/>
       <c r="E52" s="6" t="n"/>
       <c r="F52" s="6" t="n"/>
@@ -4194,7 +4189,12 @@
         </is>
       </c>
       <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+7th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D53" s="6" t="n"/>
       <c r="E53" s="6" t="n"/>
       <c r="F53" s="6" t="n"/>
@@ -4203,7 +4203,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Dr. Varshitha D N   (8 h/week, 1st hour x2)</t>
+          <t>Dr. Varshitha D N   (8 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -4228,13 +4228,13 @@
       <c r="D56" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -4256,24 +4256,14 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Machine Learning
 5th Sem - Sec A</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning Lab
-5th Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Machine Learning Lab
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="D57" s="6" t="n"/>
       <c r="E57" s="6" t="n"/>
       <c r="F57" s="6" t="n"/>
       <c r="G57" s="6" t="n"/>
@@ -4284,16 +4274,11 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Machine Learning
 5th Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Natural Language Processing
-7th Sem - Sec A</t>
         </is>
       </c>
       <c r="D58" s="6" t="n"/>
@@ -4308,13 +4293,13 @@
         </is>
       </c>
       <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+7th Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n"/>
       <c r="E59" s="6" t="n"/>
       <c r="F59" s="6" t="n"/>
       <c r="G59" s="6" t="n"/>
@@ -4325,12 +4310,22 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Natural Language Processing
-7th Sem - Sec A</t>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+5th Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lab
+5th Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Machine Learning Lab
+5th Sem - Sec A</t>
         </is>
       </c>
       <c r="E60" s="6" t="n"/>
@@ -4344,7 +4339,12 @@
         </is>
       </c>
       <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing
+7th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="D61" s="6" t="n"/>
       <c r="E61" s="6" t="n"/>
       <c r="F61" s="6" t="n"/>
@@ -4371,7 +4371,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Dr. Vijay C P   (6 h/week, 1st hour x1)</t>
+          <t>Dr. Vijay C P   (6 h/week, 1st hour x0)</t>
         </is>
       </c>
     </row>
@@ -4396,13 +4396,13 @@
       <c r="D65" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4428,7 +4428,12 @@
       <c r="C66" s="6" t="n"/>
       <c r="D66" s="6" t="n"/>
       <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+5th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="G66" s="6" t="n"/>
     </row>
     <row r="67">
@@ -4439,14 +4444,14 @@
       </c>
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec A</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
       <c r="G67" s="6" t="n"/>
     </row>
     <row r="68">
@@ -4456,38 +4461,38 @@
         </is>
       </c>
       <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec A</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
       <c r="G69" s="6" t="n"/>
     </row>
     <row r="70">
@@ -4498,13 +4503,13 @@
       </c>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec A</t>
         </is>
       </c>
+      <c r="E70" s="6" t="n"/>
       <c r="F70" s="6" t="n"/>
       <c r="G70" s="6" t="n"/>
     </row>
@@ -4514,12 +4519,7 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6" t="n"/>
       <c r="E71" s="6" t="n"/>
@@ -4529,7 +4529,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Gaurav   (5 h/week, 1st hour x2)</t>
+          <t>Gaurav   (5 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -4554,13 +4554,13 @@
       <c r="D74" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -4584,37 +4584,32 @@
       </c>
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec D</t>
+        </is>
+      </c>
       <c r="E75" s="6" t="n"/>
       <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>Management and Engineering Economics
 5th Sem - Sec B</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec D</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
       <c r="G76" s="6" t="n"/>
     </row>
     <row r="77">
@@ -4626,7 +4621,12 @@
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec D</t>
+        </is>
+      </c>
       <c r="F77" s="6" t="n"/>
       <c r="G77" s="6" t="n"/>
     </row>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec D</t>
-        </is>
-      </c>
+      <c r="D78" s="6" t="n"/>
       <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+5th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="G78" s="6" t="n"/>
     </row>
     <row r="79">
@@ -4654,7 +4654,12 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B79" s="6" t="n"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+5th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="C79" s="6" t="n"/>
       <c r="D79" s="6" t="n"/>
       <c r="E79" s="6" t="n"/>
@@ -4667,12 +4672,7 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="B80" s="6" t="n"/>
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="6" t="n"/>
       <c r="E80" s="6" t="n"/>
@@ -4682,7 +4682,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>Harshith C   (6 h/week, 1st hour x2)</t>
+          <t>Harshith C   (6 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -4707,13 +4707,13 @@
       <c r="D83" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4738,13 +4738,13 @@
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="6" t="n"/>
       <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Management and Engineering Economics
 5th Sem - Sec A</t>
         </is>
       </c>
+      <c r="F84" s="6" t="n"/>
       <c r="G84" s="6" t="n"/>
     </row>
     <row r="85">
@@ -4757,8 +4757,8 @@
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Pattern Recognition
-7th Sem - Sec A</t>
+          <t>Management and Engineering Economics
+5th Sem - Sec A</t>
         </is>
       </c>
       <c r="E85" s="6" t="n"/>
@@ -4771,51 +4771,51 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+7th Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Management and Engineering Economics
 5th Sem - Sec A</t>
         </is>
       </c>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>Pattern Recognition
 7th Sem - Sec A</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-5th Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="6" t="n"/>
       <c r="F88" s="6" t="n"/>
       <c r="G88" s="6" t="n"/>
     </row>
@@ -4825,15 +4825,15 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+7th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="C89" s="6" t="n"/>
       <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Pattern Recognition
-7th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="E89" s="6" t="n"/>
       <c r="F89" s="6" t="n"/>
       <c r="G89" s="6" t="n"/>
     </row>
@@ -4865,13 +4865,13 @@
       <c r="D92" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -4894,19 +4894,19 @@
         </is>
       </c>
       <c r="B93" s="6" t="n"/>
-      <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Pattern Recognition
 7th Sem - Sec B</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Cloud Computing
 5th Sem - Sec A</t>
         </is>
       </c>
+      <c r="E93" s="6" t="n"/>
       <c r="F93" s="6" t="n"/>
       <c r="G93" s="6" t="n"/>
     </row>
@@ -4918,16 +4918,11 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Pattern Recognition
-7th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
           <t>Cloud Computing
 5th Sem - Sec A</t>
         </is>
       </c>
+      <c r="C94" s="6" t="n"/>
       <c r="D94" s="6" t="n"/>
       <c r="E94" s="6" t="n"/>
       <c r="F94" s="6" t="n"/>
@@ -4941,12 +4936,7 @@
       </c>
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>Pattern Recognition
-7th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="D95" s="6" t="n"/>
       <c r="E95" s="6" t="n"/>
       <c r="F95" s="6" t="n"/>
       <c r="G95" s="6" t="n"/>
@@ -4960,7 +4950,12 @@
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n"/>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+7th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="F96" s="6" t="n"/>
       <c r="G96" s="6" t="n"/>
     </row>
@@ -4971,13 +4966,13 @@
         </is>
       </c>
       <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Cloud Computing
 5th Sem - Sec A</t>
         </is>
       </c>
+      <c r="D97" s="6" t="n"/>
       <c r="E97" s="6" t="n"/>
       <c r="F97" s="6" t="n"/>
       <c r="G97" s="6" t="n"/>
@@ -4990,7 +4985,12 @@
       </c>
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Pattern Recognition
+7th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="E98" s="6" t="n"/>
       <c r="F98" s="6" t="n"/>
       <c r="G98" s="6" t="n"/>
@@ -5023,13 +5023,13 @@
       <c r="D101" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -5054,47 +5054,37 @@
       <c r="B102" s="6" t="n"/>
       <c r="C102" s="6" t="n"/>
       <c r="D102" s="6" t="n"/>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+3rd Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Data Structures Laboratory
+3rd Sem - Sec B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>Data Structures
 3rd Sem - Sec B</t>
         </is>
       </c>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-3rd Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>Data Structures Laboratory
-3rd Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>UHV
-3rd Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-3rd Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5121,7 +5111,12 @@
         </is>
       </c>
       <c r="B105" s="6" t="n"/>
-      <c r="C105" s="6" t="n"/>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>UHV
+3rd Sem - Sec A</t>
+        </is>
+      </c>
       <c r="D105" s="6" t="n"/>
       <c r="E105" s="6" t="n"/>
       <c r="F105" s="6" t="n"/>
@@ -5135,7 +5130,12 @@
       </c>
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+3rd Sem - Sec B</t>
+        </is>
+      </c>
       <c r="E106" s="6" t="n"/>
       <c r="F106" s="6" t="n"/>
       <c r="G106" s="6" t="n"/>
@@ -5156,7 +5156,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>K B Manasa   (7 h/week, 1st hour x2)</t>
+          <t>K B Manasa   (7 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -5181,13 +5181,13 @@
       <c r="D110" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -5221,12 +5221,7 @@
 1st Sem - Sec F</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-1st Sem - Sec F</t>
-        </is>
-      </c>
+      <c r="D111" s="6" t="n"/>
       <c r="E111" s="6" t="n"/>
       <c r="F111" s="6" t="n"/>
       <c r="G111" s="6" t="n"/>
@@ -5240,8 +5235,8 @@
       <c r="B112" s="6" t="n"/>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Programming in C
-1st Sem - Sec F</t>
+          <t>UI/UX Design
+7th Sem - Sec B</t>
         </is>
       </c>
       <c r="D112" s="6" t="n"/>
@@ -5258,8 +5253,8 @@
       <c r="B113" s="6" t="n"/>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>UI/UX Design
-7th Sem - Sec B</t>
+          <t>Programming in C
+1st Sem - Sec F</t>
         </is>
       </c>
       <c r="D113" s="6" t="n"/>
@@ -5274,7 +5269,12 @@
         </is>
       </c>
       <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX Design
+7th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D114" s="6" t="n"/>
       <c r="E114" s="6" t="n"/>
       <c r="F114" s="6" t="n"/>
@@ -5286,14 +5286,19 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>UI/UX Design
-7th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec F</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+1st Sem - Sec F</t>
+        </is>
+      </c>
       <c r="E115" s="6" t="n"/>
       <c r="F115" s="6" t="n"/>
       <c r="G115" s="6" t="n"/>
@@ -5305,12 +5310,7 @@
         </is>
       </c>
       <c r="B116" s="6" t="n"/>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec F</t>
-        </is>
-      </c>
+      <c r="C116" s="6" t="n"/>
       <c r="D116" s="6" t="n"/>
       <c r="E116" s="6" t="n"/>
       <c r="F116" s="6" t="n"/>
@@ -5319,7 +5319,7 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Latha D U   (7 h/week, 1st hour x2)</t>
+          <t>Latha D U   (7 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -5344,13 +5344,13 @@
       <c r="D119" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -5372,23 +5372,28 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+5th Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>Machine Learning Lab
 5th Sem - Sec C</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>Machine Learning Lab
 5th Sem - Sec C</t>
         </is>
       </c>
-      <c r="D120" s="6" t="n"/>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning
-5th Sem - Sec C</t>
+          <t>Web App Development
+3rd Sem - Sec C</t>
         </is>
       </c>
       <c r="F120" s="6" t="n"/>
@@ -5401,13 +5406,13 @@
         </is>
       </c>
       <c r="B121" s="6" t="n"/>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>Machine Learning
-5th Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+3rd Sem - Sec C</t>
+        </is>
+      </c>
       <c r="E121" s="6" t="n"/>
       <c r="F121" s="6" t="n"/>
       <c r="G121" s="6" t="n"/>
@@ -5418,16 +5423,11 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>Machine Learning
 5th Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-3rd Sem - Sec C</t>
         </is>
       </c>
       <c r="D122" s="6" t="n"/>
@@ -5443,12 +5443,7 @@
       </c>
       <c r="B123" s="6" t="n"/>
       <c r="C123" s="6" t="n"/>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-3rd Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="D123" s="6" t="n"/>
       <c r="E123" s="6" t="n"/>
       <c r="F123" s="6" t="n"/>
       <c r="G123" s="6" t="n"/>
@@ -5460,7 +5455,12 @@
         </is>
       </c>
       <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Machine Learning
+5th Sem - Sec C</t>
+        </is>
+      </c>
       <c r="D124" s="6" t="n"/>
       <c r="E124" s="6" t="n"/>
       <c r="F124" s="6" t="n"/>
@@ -5482,7 +5482,7 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>Mohan Kumar G   (6 h/week, 1st hour x2)</t>
+          <t>Mohan Kumar G   (6 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -5507,13 +5507,13 @@
       <c r="D128" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -5535,18 +5535,8 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>Design Thinking
-3rd Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec E</t>
-        </is>
-      </c>
+      <c r="B129" s="6" t="n"/>
+      <c r="C129" s="6" t="n"/>
       <c r="D129" s="6" t="n"/>
       <c r="E129" s="6" t="n"/>
       <c r="F129" s="6" t="n"/>
@@ -5560,8 +5550,8 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Programming in C Laboratory
-1st Sem - Sec E</t>
+          <t>Design Thinking
+3rd Sem - Sec C</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -5588,7 +5578,12 @@
 1st Sem - Sec E</t>
         </is>
       </c>
-      <c r="D131" s="6" t="n"/>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Design Thinking
+3rd Sem - Sec C</t>
+        </is>
+      </c>
       <c r="E131" s="6" t="n"/>
       <c r="F131" s="6" t="n"/>
       <c r="G131" s="6" t="n"/>
@@ -5602,12 +5597,7 @@
       <c r="B132" s="6" t="n"/>
       <c r="C132" s="6" t="n"/>
       <c r="D132" s="6" t="n"/>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>Design Thinking
-3rd Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="E132" s="6" t="n"/>
       <c r="F132" s="6" t="n"/>
       <c r="G132" s="6" t="n"/>
     </row>
@@ -5618,8 +5608,18 @@
         </is>
       </c>
       <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec E</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+1st Sem - Sec E</t>
+        </is>
+      </c>
       <c r="E133" s="6" t="n"/>
       <c r="F133" s="6" t="n"/>
       <c r="G133" s="6" t="n"/>
@@ -5665,13 +5665,13 @@
       <c r="D137" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -5693,17 +5693,17 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B138" s="6" t="n"/>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+5th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="C138" s="6" t="n"/>
       <c r="D138" s="6" t="n"/>
       <c r="E138" s="6" t="n"/>
       <c r="F138" s="6" t="n"/>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="G138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -5719,7 +5719,12 @@
 1st Sem - Sec E</t>
         </is>
       </c>
-      <c r="E139" s="6" t="n"/>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+5th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="F139" s="6" t="n"/>
       <c r="G139" s="6" t="n"/>
     </row>
@@ -5729,14 +5734,14 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="inlineStr">
         <is>
           <t>Introduction to AI and its Applications
 1st Sem - Sec E</t>
         </is>
       </c>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
       <c r="E140" s="6" t="n"/>
       <c r="F140" s="6" t="n"/>
       <c r="G140" s="6" t="n"/>
@@ -5752,7 +5757,12 @@
       <c r="D141" s="6" t="n"/>
       <c r="E141" s="6" t="n"/>
       <c r="F141" s="6" t="n"/>
-      <c r="G141" s="6" t="n"/>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+5th Sem - Sec A</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -5761,12 +5771,7 @@
         </is>
       </c>
       <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C142" s="6" t="n"/>
       <c r="D142" s="6" t="n"/>
       <c r="E142" s="6" t="n"/>
       <c r="F142" s="6" t="n"/>
@@ -5779,12 +5784,7 @@
         </is>
       </c>
       <c r="B143" s="6" t="n"/>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-5th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C143" s="6" t="n"/>
       <c r="D143" s="6" t="n"/>
       <c r="E143" s="6" t="n"/>
       <c r="F143" s="6" t="n"/>
@@ -5818,13 +5818,13 @@
       <c r="D146" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -5850,13 +5850,13 @@
       <c r="C147" s="6" t="n"/>
       <c r="D147" s="6" t="n"/>
       <c r="E147" s="6" t="n"/>
-      <c r="F147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="n"/>
+      <c r="G147" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec B</t>
         </is>
       </c>
-      <c r="G147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -5864,17 +5864,22 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="B148" s="6" t="n"/>
       <c r="C148" s="6" t="n"/>
       <c r="D148" s="6" t="n"/>
       <c r="E148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="6" t="n"/>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>UHV
+3rd Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+5th Sem - Sec B</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -5885,27 +5890,22 @@
       <c r="B149" s="6" t="n"/>
       <c r="C149" s="6" t="n"/>
       <c r="D149" s="6" t="n"/>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>UHV
-3rd Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="F149" s="6" t="inlineStr">
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="6" t="n"/>
+      <c r="G149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec B</t>
         </is>
       </c>
-      <c r="G149" s="6" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="n"/>
       <c r="C150" s="6" t="n"/>
       <c r="D150" s="6" t="n"/>
       <c r="E150" s="6" t="n"/>
@@ -5919,7 +5919,12 @@
         </is>
       </c>
       <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+5th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D151" s="6" t="n"/>
       <c r="E151" s="6" t="n"/>
       <c r="F151" s="6" t="n"/>
@@ -5933,12 +5938,7 @@
       </c>
       <c r="B152" s="6" t="n"/>
       <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="D152" s="6" t="n"/>
       <c r="E152" s="6" t="n"/>
       <c r="F152" s="6" t="n"/>
       <c r="G152" s="6" t="n"/>
@@ -5971,13 +5971,13 @@
       <c r="D155" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -6003,12 +6003,7 @@
       <c r="C156" s="6" t="n"/>
       <c r="D156" s="6" t="n"/>
       <c r="E156" s="6" t="n"/>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>Computer Networks
-5th Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="F156" s="6" t="n"/>
       <c r="G156" s="6" t="n"/>
     </row>
     <row r="157">
@@ -6037,25 +6032,30 @@
       </c>
       <c r="B158" s="6" t="n"/>
       <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6" t="n"/>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>Computer Networks
+5th Sem - Sec C</t>
+        </is>
+      </c>
       <c r="E158" s="6" t="n"/>
       <c r="F158" s="6" t="n"/>
-      <c r="G158" s="6" t="inlineStr">
+      <c r="G158" s="6" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="n"/>
+      <c r="C159" s="6" t="n"/>
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec C</t>
         </is>
       </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="n"/>
-      <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6" t="n"/>
       <c r="E159" s="6" t="n"/>
       <c r="F159" s="6" t="n"/>
       <c r="G159" s="6" t="n"/>
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="B160" s="6" t="n"/>
-      <c r="C160" s="6" t="inlineStr">
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>Computer Networks
 5th Sem - Sec C</t>
         </is>
       </c>
-      <c r="D160" s="6" t="n"/>
       <c r="E160" s="6" t="n"/>
       <c r="F160" s="6" t="n"/>
       <c r="G160" s="6" t="n"/>
@@ -6094,7 +6094,7 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>New Faculty 4   (5 h/week, 1st hour x2)</t>
+          <t>New Faculty 4   (5 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -6119,13 +6119,13 @@
       <c r="D164" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -6147,16 +6147,16 @@
           <t>Mon</t>
         </is>
       </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec F</t>
-        </is>
-      </c>
+      <c r="B165" s="6" t="n"/>
       <c r="C165" s="6" t="n"/>
       <c r="D165" s="6" t="n"/>
       <c r="E165" s="6" t="n"/>
-      <c r="F165" s="6" t="n"/>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+5th Sem - Sec B</t>
+        </is>
+      </c>
       <c r="G165" s="6" t="n"/>
     </row>
     <row r="166">
@@ -6165,40 +6165,35 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="n"/>
+      <c r="G166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>Introduction to AI and its Applications
 1st Sem - Sec F</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-      <c r="G166" s="6" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="n"/>
       <c r="C167" s="6" t="n"/>
       <c r="D167" s="6" t="n"/>
       <c r="E167" s="6" t="n"/>
       <c r="F167" s="6" t="n"/>
-      <c r="G167" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="G167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -6221,8 +6216,18 @@
       </c>
       <c r="B169" s="6" t="n"/>
       <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-      <c r="E169" s="6" t="n"/>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>Cryptography and Network Security
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec F</t>
+        </is>
+      </c>
       <c r="F169" s="6" t="n"/>
       <c r="G169" s="6" t="n"/>
     </row>
@@ -6235,19 +6240,14 @@
       <c r="B170" s="6" t="n"/>
       <c r="C170" s="6" t="n"/>
       <c r="D170" s="6" t="n"/>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>Cryptography and Network Security
-5th Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="E170" s="6" t="n"/>
       <c r="F170" s="6" t="n"/>
       <c r="G170" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>Nidhishree G   (7 h/week, 1st hour x2)</t>
+          <t>Nidhishree G   (7 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -6272,13 +6272,13 @@
       <c r="D173" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -6323,24 +6323,14 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="B175" s="6" t="n"/>
+      <c r="C175" s="6" t="inlineStr">
         <is>
           <t>Operating System
 3rd Sem - Sec B</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C Laboratory
-1st Sem - Sec D</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec D</t>
-        </is>
-      </c>
+      <c r="D175" s="6" t="n"/>
       <c r="E175" s="6" t="n"/>
       <c r="F175" s="6" t="n"/>
       <c r="G175" s="6" t="n"/>
@@ -6354,11 +6344,16 @@
       <c r="B176" s="6" t="n"/>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>Operating System
-3rd Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="n"/>
+          <t>Programming in C Laboratory
+1st Sem - Sec D</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec D</t>
+        </is>
+      </c>
       <c r="E176" s="6" t="n"/>
       <c r="F176" s="6" t="n"/>
       <c r="G176" s="6" t="n"/>
@@ -6370,12 +6365,7 @@
         </is>
       </c>
       <c r="B177" s="6" t="n"/>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec D</t>
-        </is>
-      </c>
+      <c r="C177" s="6" t="n"/>
       <c r="D177" s="6" t="n"/>
       <c r="E177" s="6" t="n"/>
       <c r="F177" s="6" t="n"/>
@@ -6388,7 +6378,12 @@
         </is>
       </c>
       <c r="B178" s="6" t="n"/>
-      <c r="C178" s="6" t="n"/>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+3rd Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D178" s="6" t="n"/>
       <c r="E178" s="6" t="n"/>
       <c r="F178" s="6" t="n"/>
@@ -6401,7 +6396,12 @@
         </is>
       </c>
       <c r="B179" s="6" t="n"/>
-      <c r="C179" s="6" t="n"/>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec D</t>
+        </is>
+      </c>
       <c r="D179" s="6" t="n"/>
       <c r="E179" s="6" t="n"/>
       <c r="F179" s="6" t="n"/>
@@ -6410,7 +6410,7 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>Pooja N S   (6 h/week, 1st hour x2)</t>
+          <t>Pooja N S   (6 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -6435,13 +6435,13 @@
       <c r="D182" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -6464,14 +6464,14 @@
         </is>
       </c>
       <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="inlineStr">
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+      <c r="E183" s="6" t="inlineStr">
         <is>
           <t>Web App Development
 5th Sem - Sec B</t>
         </is>
       </c>
-      <c r="D183" s="6" t="n"/>
-      <c r="E183" s="6" t="n"/>
       <c r="F183" s="6" t="n"/>
       <c r="G183" s="6" t="n"/>
     </row>
@@ -6483,11 +6483,16 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
+          <t>Web App Development
+5th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
           <t>NoSQL Database
 7th Sem - Sec A</t>
         </is>
       </c>
-      <c r="C184" s="6" t="n"/>
       <c r="D184" s="6" t="n"/>
       <c r="E184" s="6" t="n"/>
       <c r="F184" s="6" t="n"/>
@@ -6500,13 +6505,13 @@
         </is>
       </c>
       <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-5th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>NoSQL Database
+7th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="E185" s="6" t="n"/>
       <c r="F185" s="6" t="n"/>
       <c r="G185" s="6" t="n"/>
@@ -6517,12 +6522,7 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>NoSQL Database
-7th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="B186" s="6" t="n"/>
       <c r="C186" s="6" t="n"/>
       <c r="D186" s="6" t="n"/>
       <c r="E186" s="6" t="n"/>
@@ -6536,13 +6536,13 @@
         </is>
       </c>
       <c r="B187" s="6" t="n"/>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C187" s="6" t="n"/>
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 7th Sem - Sec A</t>
         </is>
       </c>
-      <c r="D187" s="6" t="n"/>
       <c r="E187" s="6" t="n"/>
       <c r="F187" s="6" t="n"/>
       <c r="G187" s="6" t="n"/>
@@ -6568,7 +6568,7 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>Prashanth N   (7 h/week, 1st hour x2)</t>
+          <t>Prashanth N   (7 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -6593,13 +6593,13 @@
       <c r="D191" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -6624,16 +6624,11 @@
       <c r="B192" s="6" t="n"/>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>Programming in C Laboratory
-1st Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec C</t>
-        </is>
-      </c>
+          <t>Operating System
+3rd Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="n"/>
       <c r="E192" s="6" t="n"/>
       <c r="F192" s="6" t="n"/>
       <c r="G192" s="6" t="n"/>
@@ -6644,16 +6639,11 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B193" s="6" t="inlineStr">
+      <c r="B193" s="6" t="n"/>
+      <c r="C193" s="6" t="inlineStr">
         <is>
           <t>Operating System
 3rd Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>Programming in C
-1st Sem - Sec C</t>
         </is>
       </c>
       <c r="D193" s="6" t="n"/>
@@ -6667,14 +6657,24 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B194" s="6" t="n"/>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+3rd Sem - Sec A</t>
+        </is>
+      </c>
       <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C Laboratory
+1st Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>Programming in C
 1st Sem - Sec C</t>
         </is>
       </c>
-      <c r="D194" s="6" t="n"/>
       <c r="E194" s="6" t="n"/>
       <c r="F194" s="6" t="n"/>
       <c r="G194" s="6" t="n"/>
@@ -6685,13 +6685,13 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-3rd Sem - Sec A</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="n"/>
+      <c r="B195" s="6" t="n"/>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec C</t>
+        </is>
+      </c>
       <c r="D195" s="6" t="n"/>
       <c r="E195" s="6" t="n"/>
       <c r="F195" s="6" t="n"/>
@@ -6704,7 +6704,12 @@
         </is>
       </c>
       <c r="B196" s="6" t="n"/>
-      <c r="C196" s="6" t="n"/>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>Programming in C
+1st Sem - Sec C</t>
+        </is>
+      </c>
       <c r="D196" s="6" t="n"/>
       <c r="E196" s="6" t="n"/>
       <c r="F196" s="6" t="n"/>
@@ -6717,12 +6722,7 @@
         </is>
       </c>
       <c r="B197" s="6" t="n"/>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-3rd Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C197" s="6" t="n"/>
       <c r="D197" s="6" t="n"/>
       <c r="E197" s="6" t="n"/>
       <c r="F197" s="6" t="n"/>
@@ -6756,13 +6756,13 @@
       <c r="D200" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -6808,51 +6808,46 @@
         </is>
       </c>
       <c r="B202" s="6" t="n"/>
-      <c r="C202" s="6" t="n"/>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+3rd Sem - Sec C</t>
+        </is>
+      </c>
       <c r="D202" s="6" t="n"/>
       <c r="E202" s="6" t="n"/>
       <c r="F202" s="6" t="n"/>
-      <c r="G202" s="6" t="inlineStr">
+      <c r="G202" s="6" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="n"/>
+      <c r="C203" s="6" t="n"/>
+      <c r="D203" s="6" t="n"/>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Operating System
+3rd Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="n"/>
+      <c r="G203" s="6" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="n"/>
+      <c r="C204" s="6" t="inlineStr">
         <is>
           <t>Management and Engineering Economics
 5th Sem - Sec C</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-3rd Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>Management and Engineering Economics
-5th Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="D203" s="6" t="n"/>
-      <c r="E203" s="6" t="n"/>
-      <c r="F203" s="6" t="n"/>
-      <c r="G203" s="6" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="n"/>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>Operating System
-3rd Sem - Sec C</t>
         </is>
       </c>
       <c r="D204" s="6" t="n"/>
@@ -6866,7 +6861,12 @@
           <t>Fri</t>
         </is>
       </c>
-      <c r="B205" s="6" t="n"/>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>Management and Engineering Economics
+5th Sem - Sec C</t>
+        </is>
+      </c>
       <c r="C205" s="6" t="n"/>
       <c r="D205" s="6" t="n"/>
       <c r="E205" s="6" t="n"/>
@@ -6914,13 +6914,13 @@
       <c r="D209" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -6960,49 +6960,39 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B211" s="6" t="inlineStr">
+      <c r="B211" s="6" t="n"/>
+      <c r="C211" s="6" t="n"/>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+5th Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>DevOps Laboratory
+5th Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="n"/>
+      <c r="G211" s="6" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>Oops with Java
 3rd Sem - Sec C</t>
         </is>
       </c>
-      <c r="C211" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-3rd Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="D211" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-3rd Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="n"/>
-      <c r="F211" s="6" t="n"/>
-      <c r="G211" s="6" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="n"/>
       <c r="C212" s="6" t="n"/>
       <c r="D212" s="6" t="n"/>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-5th Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr">
-        <is>
-          <t>DevOps Laboratory
-5th Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="E212" s="6" t="n"/>
+      <c r="F212" s="6" t="n"/>
       <c r="G212" s="6" t="n"/>
     </row>
     <row r="213">
@@ -7014,14 +7004,24 @@
       <c r="B213" s="6" t="n"/>
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6" t="n"/>
-      <c r="E213" s="6" t="n"/>
-      <c r="F213" s="6" t="inlineStr">
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+3rd Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+3rd Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
         <is>
           <t>Oops with Java
 3rd Sem - Sec C</t>
         </is>
       </c>
-      <c r="G213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -7077,13 +7077,13 @@
       <c r="D218" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -7108,17 +7108,22 @@
       <c r="B219" s="6" t="n"/>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="D219" s="6" t="inlineStr">
-        <is>
           <t>Oops with Java
 3rd Sem - Sec B</t>
         </is>
       </c>
-      <c r="E219" s="6" t="n"/>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+3rd Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>Java Laboratory
+3rd Sem - Sec B</t>
+        </is>
+      </c>
       <c r="F219" s="6" t="n"/>
       <c r="G219" s="6" t="n"/>
     </row>
@@ -7128,44 +7133,34 @@
           <t>Tue</t>
         </is>
       </c>
-      <c r="B220" s="6" t="n"/>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+3rd Sem - Sec B</t>
+        </is>
+      </c>
       <c r="C220" s="6" t="n"/>
       <c r="D220" s="6" t="n"/>
       <c r="E220" s="6" t="n"/>
-      <c r="F220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="n"/>
+      <c r="G220" s="6" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="n"/>
+      <c r="C221" s="6" t="inlineStr">
         <is>
           <t>Oops with Java
 3rd Sem - Sec B</t>
         </is>
       </c>
-      <c r="G220" s="6" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="5" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="n"/>
-      <c r="C221" s="6" t="n"/>
-      <c r="D221" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-3rd Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-3rd Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr">
-        <is>
-          <t>Java Laboratory
-3rd Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="D221" s="6" t="n"/>
+      <c r="E221" s="6" t="n"/>
+      <c r="F221" s="6" t="n"/>
       <c r="G221" s="6" t="n"/>
     </row>
     <row r="222">
@@ -7174,13 +7169,13 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B222" s="6" t="inlineStr">
+      <c r="B222" s="6" t="n"/>
+      <c r="C222" s="6" t="inlineStr">
         <is>
           <t>Introduction to AI and its Applications
 1st Sem - Sec B</t>
         </is>
       </c>
-      <c r="C222" s="6" t="n"/>
       <c r="D222" s="6" t="n"/>
       <c r="E222" s="6" t="n"/>
       <c r="F222" s="6" t="n"/>
@@ -7206,7 +7201,12 @@
         </is>
       </c>
       <c r="B224" s="6" t="n"/>
-      <c r="C224" s="6" t="n"/>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec B</t>
+        </is>
+      </c>
       <c r="D224" s="6" t="n"/>
       <c r="E224" s="6" t="n"/>
       <c r="F224" s="6" t="n"/>
@@ -7240,13 +7240,13 @@
       <c r="D227" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -7270,11 +7270,16 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
+          <t>Oops with Java
+3rd Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
           <t>Introduction to AI and its Applications
 1st Sem - Sec A</t>
         </is>
       </c>
-      <c r="C228" s="6" t="n"/>
       <c r="D228" s="6" t="n"/>
       <c r="E228" s="6" t="n"/>
       <c r="F228" s="6" t="n"/>
@@ -7289,23 +7294,28 @@
       <c r="B229" s="6" t="n"/>
       <c r="C229" s="6" t="inlineStr">
         <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
           <t>Oops with Java
 3rd Sem - Sec A</t>
         </is>
       </c>
-      <c r="D229" s="7" t="inlineStr">
+      <c r="E229" s="7" t="inlineStr">
         <is>
           <t>Java Laboratory
 3rd Sem - Sec A</t>
         </is>
       </c>
-      <c r="E229" s="7" t="inlineStr">
+      <c r="F229" s="7" t="inlineStr">
         <is>
           <t>Java Laboratory
 3rd Sem - Sec A</t>
         </is>
       </c>
-      <c r="F229" s="6" t="n"/>
       <c r="G229" s="6" t="n"/>
     </row>
     <row r="230">
@@ -7315,13 +7325,13 @@
         </is>
       </c>
       <c r="B230" s="6" t="n"/>
-      <c r="C230" s="6" t="n"/>
-      <c r="D230" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>Oops with Java
+3rd Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="n"/>
       <c r="E230" s="6" t="n"/>
       <c r="F230" s="6" t="n"/>
       <c r="G230" s="6" t="n"/>
@@ -7333,12 +7343,7 @@
         </is>
       </c>
       <c r="B231" s="6" t="n"/>
-      <c r="C231" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-3rd Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C231" s="6" t="n"/>
       <c r="D231" s="6" t="n"/>
       <c r="E231" s="6" t="n"/>
       <c r="F231" s="6" t="n"/>
@@ -7365,12 +7370,7 @@
       </c>
       <c r="B233" s="6" t="n"/>
       <c r="C233" s="6" t="n"/>
-      <c r="D233" s="6" t="inlineStr">
-        <is>
-          <t>Oops with Java
-3rd Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="D233" s="6" t="n"/>
       <c r="E233" s="6" t="n"/>
       <c r="F233" s="6" t="n"/>
       <c r="G233" s="6" t="n"/>
@@ -7403,13 +7403,13 @@
       <c r="D236" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -7435,38 +7435,33 @@
       <c r="C237" s="6" t="n"/>
       <c r="D237" s="6" t="inlineStr">
         <is>
+          <t>NoSQL Database
+7th Sem - Sec B</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
           <t>Web App Development
 5th Sem - Sec C</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="n"/>
+      <c r="G237" s="6" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 7th Sem - Sec B</t>
         </is>
       </c>
-      <c r="F237" s="6" t="n"/>
-      <c r="G237" s="6" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="5" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="n"/>
-      <c r="C238" s="6" t="inlineStr">
-        <is>
-          <t>NoSQL Database
-7th Sem - Sec B</t>
-        </is>
-      </c>
-      <c r="D238" s="6" t="inlineStr">
-        <is>
-          <t>Web App Development
-5th Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="C238" s="6" t="n"/>
+      <c r="D238" s="6" t="n"/>
       <c r="E238" s="6" t="n"/>
       <c r="F238" s="6" t="n"/>
       <c r="G238" s="6" t="n"/>
@@ -7477,27 +7472,32 @@
           <t>Wed</t>
         </is>
       </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B239" s="6" t="n"/>
+      <c r="C239" s="6" t="n"/>
+      <c r="D239" s="6" t="n"/>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>Web App Development
+5th Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="F239" s="6" t="n"/>
+      <c r="G239" s="6" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="n"/>
+      <c r="C240" s="6" t="n"/>
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 7th Sem - Sec B</t>
         </is>
       </c>
-      <c r="C239" s="6" t="n"/>
-      <c r="D239" s="6" t="n"/>
-      <c r="E239" s="6" t="n"/>
-      <c r="F239" s="6" t="n"/>
-      <c r="G239" s="6" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="n"/>
-      <c r="C240" s="6" t="n"/>
-      <c r="D240" s="6" t="n"/>
       <c r="E240" s="6" t="n"/>
       <c r="F240" s="6" t="n"/>
       <c r="G240" s="6" t="n"/>
@@ -7509,13 +7509,13 @@
         </is>
       </c>
       <c r="B241" s="6" t="n"/>
-      <c r="C241" s="6" t="inlineStr">
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="6" t="inlineStr">
         <is>
           <t>NoSQL Database
 7th Sem - Sec B</t>
         </is>
       </c>
-      <c r="D241" s="6" t="n"/>
       <c r="E241" s="6" t="n"/>
       <c r="F241" s="6" t="n"/>
       <c r="G241" s="6" t="n"/>
@@ -7536,7 +7536,7 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>Soumya G V   (6 h/week, 1st hour x2)</t>
+          <t>Soumya G V   (6 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -7561,13 +7561,13 @@
       <c r="D245" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -7593,12 +7593,7 @@
       <c r="C246" s="6" t="n"/>
       <c r="D246" s="6" t="n"/>
       <c r="E246" s="6" t="n"/>
-      <c r="F246" s="6" t="inlineStr">
-        <is>
-          <t>UHV
-3rd Sem - Sec B</t>
-        </is>
-      </c>
+      <c r="F246" s="6" t="n"/>
       <c r="G246" s="6" t="n"/>
     </row>
     <row r="247">
@@ -7609,19 +7604,14 @@
       </c>
       <c r="B247" s="6" t="n"/>
       <c r="C247" s="6" t="n"/>
-      <c r="D247" s="6" t="n"/>
-      <c r="E247" s="7" t="inlineStr">
-        <is>
-          <t>IoT Skill Lab
-3rd Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="F247" s="7" t="inlineStr">
-        <is>
-          <t>IoT Skill Lab
-3rd Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>Big Data Analytics
+7th Sem - Sec A</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="n"/>
+      <c r="F247" s="6" t="n"/>
       <c r="G247" s="6" t="n"/>
     </row>
     <row r="248">
@@ -7634,7 +7624,12 @@
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6" t="n"/>
       <c r="E248" s="6" t="n"/>
-      <c r="F248" s="6" t="n"/>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>Big Data Analytics
+7th Sem - Sec A</t>
+        </is>
+      </c>
       <c r="G248" s="6" t="n"/>
     </row>
     <row r="249">
@@ -7644,14 +7639,19 @@
         </is>
       </c>
       <c r="B249" s="6" t="n"/>
-      <c r="C249" s="6" t="n"/>
-      <c r="D249" s="6" t="n"/>
-      <c r="E249" s="6" t="inlineStr">
-        <is>
-          <t>Big Data Analytics
-7th Sem - Sec A</t>
-        </is>
-      </c>
+      <c r="C249" s="7" t="inlineStr">
+        <is>
+          <t>IoT Skill Lab
+3rd Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>IoT Skill Lab
+3rd Sem - Sec C</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="n"/>
       <c r="F249" s="6" t="n"/>
       <c r="G249" s="6" t="n"/>
     </row>
@@ -7663,8 +7663,8 @@
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>Big Data Analytics
-7th Sem - Sec A</t>
+          <t>UHV
+3rd Sem - Sec B</t>
         </is>
       </c>
       <c r="C250" s="6" t="n"/>
@@ -7679,22 +7679,22 @@
           <t>Sat</t>
         </is>
       </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B251" s="6" t="n"/>
+      <c r="C251" s="6" t="n"/>
+      <c r="D251" s="6" t="n"/>
+      <c r="E251" s="6" t="inlineStr">
         <is>
           <t>Big Data Analytics
 7th Sem - Sec A</t>
         </is>
       </c>
-      <c r="C251" s="6" t="n"/>
-      <c r="D251" s="6" t="n"/>
-      <c r="E251" s="6" t="n"/>
       <c r="F251" s="6" t="n"/>
       <c r="G251" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>Vignesh T V   (7 h/week, 1st hour x2)</t>
+          <t>Vignesh T V   (7 h/week, 1st hour x1)</t>
         </is>
       </c>
     </row>
@@ -7719,13 +7719,13 @@
       <c r="D254" s="4" t="inlineStr">
         <is>
           <t>P3
-11:15-12:15</t>
+11:30-12:30</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
           <t>P4
-13:00-14:00</t>
+12:30-13:30</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -7749,28 +7749,23 @@
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="C255" s="6" t="inlineStr">
-        <is>
           <t>Data Structures
 3rd Sem - Sec C</t>
         </is>
       </c>
-      <c r="D255" s="7" t="inlineStr">
+      <c r="C255" s="7" t="inlineStr">
         <is>
           <t>Data Structures Laboratory
 3rd Sem - Sec C</t>
         </is>
       </c>
-      <c r="E255" s="7" t="inlineStr">
+      <c r="D255" s="7" t="inlineStr">
         <is>
           <t>Data Structures Laboratory
 3rd Sem - Sec C</t>
         </is>
       </c>
+      <c r="E255" s="6" t="n"/>
       <c r="F255" s="6" t="n"/>
       <c r="G255" s="6" t="n"/>
     </row>
@@ -7782,13 +7777,13 @@
       </c>
       <c r="B256" s="6" t="n"/>
       <c r="C256" s="6" t="n"/>
-      <c r="D256" s="6" t="inlineStr">
-        <is>
-          <t>Introduction to AI and its Applications
-1st Sem - Sec C</t>
-        </is>
-      </c>
-      <c r="E256" s="6" t="n"/>
+      <c r="D256" s="6" t="n"/>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
+          <t>Data Structures
+3rd Sem - Sec C</t>
+        </is>
+      </c>
       <c r="F256" s="6" t="n"/>
       <c r="G256" s="6" t="n"/>
     </row>
@@ -7799,13 +7794,13 @@
         </is>
       </c>
       <c r="B257" s="6" t="n"/>
-      <c r="C257" s="6" t="n"/>
-      <c r="D257" s="6" t="inlineStr">
+      <c r="C257" s="6" t="inlineStr">
         <is>
           <t>Data Structures
 3rd Sem - Sec C</t>
         </is>
       </c>
+      <c r="D257" s="6" t="n"/>
       <c r="E257" s="6" t="n"/>
       <c r="F257" s="6" t="n"/>
       <c r="G257" s="6" t="n"/>
@@ -7816,14 +7811,14 @@
           <t>Thu</t>
         </is>
       </c>
-      <c r="B258" s="6" t="inlineStr">
-        <is>
-          <t>Data Structures
-3rd Sem - Sec C</t>
-        </is>
-      </c>
+      <c r="B258" s="6" t="n"/>
       <c r="C258" s="6" t="n"/>
-      <c r="D258" s="6" t="n"/>
+      <c r="D258" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec C</t>
+        </is>
+      </c>
       <c r="E258" s="6" t="n"/>
       <c r="F258" s="6" t="n"/>
       <c r="G258" s="6" t="n"/>
@@ -7836,7 +7831,12 @@
       </c>
       <c r="B259" s="6" t="n"/>
       <c r="C259" s="6" t="n"/>
-      <c r="D259" s="6" t="n"/>
+      <c r="D259" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to AI and its Applications
+1st Sem - Sec C</t>
+        </is>
+      </c>
       <c r="E259" s="6" t="n"/>
       <c r="F259" s="6" t="n"/>
       <c r="G259" s="6" t="n"/>
@@ -7933,11 +7933,11 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Seema H R (Mon)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7960,11 +7960,11 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dr. C Manjunath (Mon)</t>
+          <t>Dr. C Manjunath (Sat)</t>
         </is>
       </c>
     </row>
@@ -7987,11 +7987,11 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vignesh T V (Mon)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8014,11 +8014,11 @@
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gaurav (Tue)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8041,11 +8041,11 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mohan Kumar G (Tue)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8068,11 +8068,11 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>New Faculty 4 (Mon)</t>
+          <t>New Faculty 4 (Wed)</t>
         </is>
       </c>
     </row>
@@ -8092,14 +8092,14 @@
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prashanth N (Tue)</t>
+          <t>Seema H R (Mon)</t>
         </is>
       </c>
     </row>
@@ -8119,10 +8119,10 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -8149,11 +8149,11 @@
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mohan Kumar G (Mon)</t>
+          <t>Vignesh T V (Mon)</t>
         </is>
       </c>
     </row>
@@ -8173,14 +8173,14 @@
         <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dr. Varshitha D N (Mon)</t>
+          <t>New Faculty 1 (Mon)</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -8257,11 +8257,11 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pooja N S (Tue)</t>
+          <t>Harshith C (Sat)</t>
         </is>
       </c>
     </row>
@@ -8281,10 +8281,10 @@
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -8449,7 +8449,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -8483,7 +8483,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -8548,7 +8548,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -8582,10 +8582,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -8619,7 +8619,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -8650,10 +8650,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -8687,7 +8687,7 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -8718,7 +8718,7 @@
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -8752,7 +8752,7 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -8789,7 +8789,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -8823,7 +8823,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -8854,10 +8854,10 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -8888,7 +8888,7 @@
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -8993,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -9024,10 +9024,10 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -9058,10 +9058,10 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -9095,7 +9095,7 @@
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -9126,7 +9126,7 @@
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -9194,7 +9194,7 @@
         <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -9228,7 +9228,7 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -9262,7 +9262,7 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -9299,7 +9299,7 @@
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -9330,10 +9330,10 @@
         <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>course:BCICN502</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>course:BCICN502</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>course:BCICN502</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>rule</t>
         </is>
       </c>
     </row>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>limit 2 per faculty, 28 faculty hold a 1st hour</t>
+          <t>limit 2 per faculty, 27 faculty hold a 1st hour</t>
         </is>
       </c>
     </row>
